--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/03-ganhos-e-gastos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/03-ganhos-e-gastos.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Rafa Design é uma pessoa fictícia. Os valores são inventados. Apague-os antes de começar.</t>
+          <t>Rafa Design é uma pessoa fictícia, designer autônoma. Os valores são inventados. Apague-os antes de começar. As outras planilhas do kit usam a Prisma Comunicação, uma empresa: aqui o exemplo é de uma pessoa só de propósito, porque esta planilha também serve para o dinheiro pessoal e para negócio de uma pessoa. A mesma estrutura funciona nos dois casos.</t>
         </is>
       </c>
     </row>
@@ -2582,10 +2582,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <dataValidations count="2">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>=Config!$H$5:$H$16</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$5,0,0,MAX(1,COUNTA(Config!$F$5:$F$16)),1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -12803,22 +12803,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="B5:B504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Receita,Despesa"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$J$5,0,0,MAX(1,COUNTA(Config!$D$5:$D$16)+COUNTA(Config!$F$5:$F$16)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Pix,Cartão,Dinheiro,Boleto,Transferência"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="E5:E504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/03-ganhos-e-gastos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/03-ganhos-e-gastos.xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Em Painel, escolha o mês em Config e veja: entrou, saiu, sobrou, saldo, a pagar, reserva e as categorias com barra. O que você guarda na categoria de reserva sai da conta, mas não conta como gasto: fica fora da média de despesas e soma aos meses de reserva.</t>
+          <t>Em Painel, escolha o mês em Config e veja: entrou, saiu, sobrou, saldo, a receber, a pagar, reserva e as categorias com barra. O painel é de caixa: conta só o lançamento marcado Pago? = Sim, e o que falta pagar ou receber aparece nos dois quadros próprios. O que você guarda na categoria de reserva sai da conta, mas não conta como gasto: fica fora da média de despesas e soma aos meses de reserva.</t>
         </is>
       </c>
     </row>
@@ -1127,8 +1127,8 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>IFERROR((SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$A$5:$A$504,"&gt;="&amp;DATE(Config!$B$5,Config!$B$7-2,1),Lançamentos!$A$5:$A$504,"&lt;="&amp;DATE(Config!$B$5,Config!$B$7+1,0))-SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$B$10,Lançamentos!$A$5:$A$504,"&gt;="&amp;DATE(Config!$B$5,Config!$B$7-2,1),Lançamentos!$A$5:$A$504,"&lt;="&amp;DATE(Config!$B$5,Config!$B$7+1,0)))/3,0)</f>
-        <v>4131.9</v>
+        <f>IFERROR((SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$A$5:$A$504,"&gt;="&amp;DATE(Config!$B$5,Config!$B$7-2,1),Lançamentos!$A$5:$A$504,"&lt;="&amp;DATE(Config!$B$5,Config!$B$7+1,0))-SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$B$10,Lançamentos!$A$5:$A$504,"&gt;="&amp;DATE(Config!$B$5,Config!$B$7-2,1),Lançamentos!$A$5:$A$504,"&lt;="&amp;DATE(Config!$B$5,Config!$B$7+1,0)))/3,0)</f>
+        <v>4011.23333333333</v>
       </c>
     </row>
     <row r="9">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$B$10,Lançamentos!$A$5:$A$504,"&lt;="&amp;DATE(Config!$B$5,Config!$B$7+1,0))</f>
+        <f>SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$B$10,Lançamentos!$A$5:$A$504,"&lt;="&amp;DATE(Config!$B$5,Config!$B$7+1,0))</f>
         <v>1500</v>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C10" s="24">
         <f>IF(C8&gt;0,(G5+C9)/C8,0)</f>
-        <v>2.53788813862872</v>
+        <v>2.61423336131032</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1187,8 +1187,8 @@
     </row>
     <row r="13">
       <c r="A13" s="27" t="str">
-        <f>"O que vai para a categoria "&amp;Config!$B$10&amp;" sai da conta (entra em Saiu no mês), mas não é gasto: fica fora da média e soma ao cálculo de meses de reserva."</f>
-        <v>O que vai para a categoria Reserva sai da conta (entra em Saiu no mês), mas não é gasto: fica fora da média e soma ao cálculo de meses de reserva.</v>
+        <f>"Todo este painel é de caixa: entra só o lançamento com Pago? = Sim. O que ainda falta pagar ou receber aparece nos dois quadros do alto. O que vai para a categoria "&amp;Config!$B$10&amp;" sai da conta (entra em Saiu no mês), mas não é gasto: fica fora da média e soma ao cálculo de meses de reserva."</f>
+        <v>Todo este painel é de caixa: entra só o lançamento com Pago? = Sim. O que ainda falta pagar ou receber aparece nos dois quadros do alto. O que vai para a categoria Reserva sai da conta (entra em Saiu no mês), mas não é gasto: fica fora da média e soma ao cálculo de meses de reserva.</v>
       </c>
     </row>
     <row r="15">
@@ -1234,7 +1234,7 @@
         <v>Moradia</v>
       </c>
       <c r="B17" s="32">
-        <f>IF(Config!$F$5="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$5,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$5="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$5,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>1660</v>
       </c>
       <c r="C17" s="33">
@@ -1242,7 +1242,7 @@
         <v>0.397709576175759</v>
       </c>
       <c r="D17" s="32">
-        <f>IF(Config!$F$5="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$5,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$5,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$5="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$5,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$5,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>1660</v>
       </c>
       <c r="E17" s="34" t="str">
@@ -1259,7 +1259,7 @@
         <v>Alimentação</v>
       </c>
       <c r="B18" s="32">
-        <f>IF(Config!$F$6="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$6,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$6="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$6,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>900</v>
       </c>
       <c r="C18" s="33">
@@ -1267,7 +1267,7 @@
         <v>0.215625673830231</v>
       </c>
       <c r="D18" s="32">
-        <f>IF(Config!$F$6="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$6,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$6,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$6="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$6,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$6,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>851</v>
       </c>
       <c r="E18" s="34" t="str">
@@ -1284,7 +1284,7 @@
         <v>Transporte</v>
       </c>
       <c r="B19" s="32">
-        <f>IF(Config!$F$7="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$7,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$7="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$7,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>187</v>
       </c>
       <c r="C19" s="33">
@@ -1292,7 +1292,7 @@
         <v>0.0448022233402813</v>
       </c>
       <c r="D19" s="32">
-        <f>IF(Config!$F$7="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$7,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$7,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$7="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$7,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$7,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>202</v>
       </c>
       <c r="E19" s="34" t="str">
@@ -1309,7 +1309,7 @@
         <v>Ferramentas e assinaturas</v>
       </c>
       <c r="B20" s="32">
-        <f>IF(Config!$F$8="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$8,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$8="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$8,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>189</v>
       </c>
       <c r="C20" s="33">
@@ -1317,7 +1317,7 @@
         <v>0.0452813915043485</v>
       </c>
       <c r="D20" s="32">
-        <f>IF(Config!$F$8="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$8,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$8,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$8="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$8,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$8,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>189</v>
       </c>
       <c r="E20" s="34" t="str">
@@ -1334,15 +1334,15 @@
         <v>Impostos e taxas</v>
       </c>
       <c r="B21" s="32">
-        <f>IF(Config!$F$9="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$9,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
-        <v>145.9</v>
+        <f>IF(Config!$F$9="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$9,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <v>80.9</v>
       </c>
       <c r="C21" s="33">
         <f>IF(OR(Config!$F$9="",$C$5=0),"",B21/$C$5)</f>
-        <v>0.0349553175687007</v>
+        <v>0.0193823522365174</v>
       </c>
       <c r="D21" s="32">
-        <f>IF(Config!$F$9="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$9,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$9,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$9="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$9,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$9,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>80.9</v>
       </c>
       <c r="E21" s="34" t="str">
@@ -1359,7 +1359,7 @@
         <v>Marketing</v>
       </c>
       <c r="B22" s="32">
-        <f>IF(Config!$F$10="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$10,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$10="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$10,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>150</v>
       </c>
       <c r="C22" s="33">
@@ -1367,7 +1367,7 @@
         <v>0.0359376123050385</v>
       </c>
       <c r="D22" s="32">
-        <f>IF(Config!$F$10="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$10,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$10,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$10="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$10,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$10,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>150</v>
       </c>
       <c r="E22" s="34" t="str">
@@ -1384,7 +1384,7 @@
         <v>Equipamentos</v>
       </c>
       <c r="B23" s="32">
-        <f>IF(Config!$F$11="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$11,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$11="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$11,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>0</v>
       </c>
       <c r="C23" s="33">
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="32">
-        <f>IF(Config!$F$11="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$11,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$11,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$11="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$11,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$11,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>890</v>
       </c>
       <c r="E23" s="34">
@@ -1409,7 +1409,7 @@
         <v>Saúde</v>
       </c>
       <c r="B24" s="32">
-        <f>IF(Config!$F$12="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$12,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$12="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$12,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>390</v>
       </c>
       <c r="C24" s="33">
@@ -1417,7 +1417,7 @@
         <v>0.0934377919931</v>
       </c>
       <c r="D24" s="32">
-        <f>IF(Config!$F$12="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$12,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$12,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$12="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$12,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$12,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>390</v>
       </c>
       <c r="E24" s="34" t="str">
@@ -1434,7 +1434,7 @@
         <v>Lazer</v>
       </c>
       <c r="B25" s="32">
-        <f>IF(Config!$F$13="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$13,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$13="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$13,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>117</v>
       </c>
       <c r="C25" s="33">
@@ -1442,7 +1442,7 @@
         <v>0.02803133759793</v>
       </c>
       <c r="D25" s="32">
-        <f>IF(Config!$F$13="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$13,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$13,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$13="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$13,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$13,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>178</v>
       </c>
       <c r="E25" s="34" t="str">
@@ -1459,20 +1459,20 @@
         <v>Educação</v>
       </c>
       <c r="B26" s="32">
-        <f>IF(Config!$F$14="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$14,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
-        <v>297</v>
+        <f>IF(Config!$F$14="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$14,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <v>0</v>
       </c>
       <c r="C26" s="33">
         <f>IF(OR(Config!$F$14="",$C$5=0),"",B26/$C$5)</f>
-        <v>0.0711564723639761</v>
+        <v>0</v>
       </c>
       <c r="D26" s="32">
-        <f>IF(Config!$F$14="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$14,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$14,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$14="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$14,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$14,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="34" t="str">
+      <c r="E26" s="34">
         <f>IF(C26="","",REPT("█",ROUND(C26*40,0)))</f>
-        <v>███</v>
+        <v/>
       </c>
       <c r="F26" s="29" t="n"/>
       <c r="G26" s="29" t="n"/>
@@ -1484,7 +1484,7 @@
         <v>Reserva</v>
       </c>
       <c r="B27" s="32">
-        <f>IF(Config!$F$15="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$15,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$15="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$15,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>500</v>
       </c>
       <c r="C27" s="33">
@@ -1492,7 +1492,7 @@
         <v>0.119792041016795</v>
       </c>
       <c r="D27" s="32">
-        <f>IF(Config!$F$15="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$15,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$15,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$15="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$15,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$15,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>500</v>
       </c>
       <c r="E27" s="34" t="str">
@@ -1509,7 +1509,7 @@
         <v>Outras despesas</v>
       </c>
       <c r="B28" s="32">
-        <f>IF(Config!$F$16="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$16,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$F$16="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$16,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>0</v>
       </c>
       <c r="C28" s="33">
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="32">
-        <f>IF(Config!$F$16="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$16,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$C$5:$C$504,Config!$F$16,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$F$16="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$16,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Despesa",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$F$16,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>0</v>
       </c>
       <c r="E28" s="34">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B29" s="36">
         <f>SUM(B17:B28)</f>
-        <v>4535.9</v>
+        <v>4173.9</v>
       </c>
       <c r="D29" s="36">
         <f>SUM(D17:D28)</f>
@@ -1578,7 +1578,7 @@
         <v>Serviços</v>
       </c>
       <c r="B33" s="32">
-        <f>IF(Config!$D$5="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$5,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$5="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$5,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>6350</v>
       </c>
       <c r="C33" s="33">
@@ -1586,7 +1586,7 @@
         <v>0.952023988005997</v>
       </c>
       <c r="D33" s="32">
-        <f>IF(Config!$D$5="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$5,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$5,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$5="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$5,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$5,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>7400</v>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
         <v>Produtos</v>
       </c>
       <c r="B34" s="32">
-        <f>IF(Config!$D$6="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$6,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$6="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$6,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>320</v>
       </c>
       <c r="C34" s="33">
@@ -1604,7 +1604,7 @@
         <v>0.047976011994003</v>
       </c>
       <c r="D34" s="32">
-        <f>IF(Config!$D$6="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$6,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$6,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$6="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$6,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$6,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>0</v>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
         <v>Comissões</v>
       </c>
       <c r="B35" s="32">
-        <f>IF(Config!$D$7="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$7,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$7="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$7,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>0</v>
       </c>
       <c r="C35" s="33">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="32">
-        <f>IF(Config!$D$7="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$7,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$7,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$7="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$7,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$7,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>0</v>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
         <v>Outras receitas</v>
       </c>
       <c r="B36" s="32">
-        <f>IF(Config!$D$8="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$8,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$8="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$8,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v>0</v>
       </c>
       <c r="C36" s="33">
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="32">
-        <f>IF(Config!$D$8="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$8,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$8,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$8="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$8,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$8,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v>0</v>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         <v/>
       </c>
       <c r="B37" s="32">
-        <f>IF(Config!$D$9="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$9,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$9="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$9,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C37" s="33">
@@ -1658,7 +1658,7 @@
         <v/>
       </c>
       <c r="D37" s="32">
-        <f>IF(Config!$D$9="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$9,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$9,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$9="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$9,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$9,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
         <v/>
       </c>
       <c r="B38" s="32">
-        <f>IF(Config!$D$10="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$10,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$10="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$10,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C38" s="33">
@@ -1676,7 +1676,7 @@
         <v/>
       </c>
       <c r="D38" s="32">
-        <f>IF(Config!$D$10="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$10,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$10,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$10="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$10,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$10,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         <v/>
       </c>
       <c r="B39" s="32">
-        <f>IF(Config!$D$11="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$11,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$11="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$11,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C39" s="33">
@@ -1694,7 +1694,7 @@
         <v/>
       </c>
       <c r="D39" s="32">
-        <f>IF(Config!$D$11="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$11,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$11,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$11="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$11,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$11,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="B40" s="32">
-        <f>IF(Config!$D$12="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$12,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$12="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$12,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C40" s="33">
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="D40" s="32">
-        <f>IF(Config!$D$12="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$12,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$12,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$12="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$12,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$12,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="B41" s="32">
-        <f>IF(Config!$D$13="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$13,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$13="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$13,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C41" s="33">
@@ -1730,7 +1730,7 @@
         <v/>
       </c>
       <c r="D41" s="32">
-        <f>IF(Config!$D$13="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$13,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$13,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$13="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$13,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$13,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
         <v/>
       </c>
       <c r="B42" s="32">
-        <f>IF(Config!$D$14="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$14,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$14="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$14,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C42" s="33">
@@ -1748,7 +1748,7 @@
         <v/>
       </c>
       <c r="D42" s="32">
-        <f>IF(Config!$D$14="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$14,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$14,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$14="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$14,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$14,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
         <v/>
       </c>
       <c r="B43" s="32">
-        <f>IF(Config!$D$15="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$15,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$15="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$15,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C43" s="33">
@@ -1766,7 +1766,7 @@
         <v/>
       </c>
       <c r="D43" s="32">
-        <f>IF(Config!$D$15="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$15,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$15,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$15="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$15,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$15,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         <v/>
       </c>
       <c r="B44" s="32">
-        <f>IF(Config!$D$16="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$16,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
+        <f>IF(Config!$D$16="","",SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$16,Lançamentos!$I$5:$I$504,Config!$B$7,Lançamentos!$J$5:$J$504,Config!$B$5))</f>
         <v/>
       </c>
       <c r="C44" s="33">
@@ -1784,7 +1784,7 @@
         <v/>
       </c>
       <c r="D44" s="32">
-        <f>IF(Config!$D$16="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$16,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$C$5:$C$504,Config!$D$16,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
+        <f>IF(Config!$D$16="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$16,Lançamentos!$I$5:$I$504,12,Lançamentos!$J$5:$J$504,Config!$B$5-1),SUMIFS(Lançamentos!$E$5:$E$504,Lançamentos!$B$5:$B$504,"Receita",Lançamentos!$G$5:$G$504,"Sim",Lançamentos!$C$5:$C$504,Config!$D$16,Lançamentos!$I$5:$I$504,Config!$B$7-1,Lançamentos!$J$5:$J$504,Config!$B$5)))</f>
         <v/>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/03-ganhos-e-gastos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/03-ganhos-e-gastos.xlsx
@@ -264,23 +264,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1026,8 +1026,10 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="4" customWidth="1" min="9" max="9"/>
-    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1043,7 +1045,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Entrou no mês</t>
@@ -2115,10 +2117,10 @@
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="E25:H25"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E22:H22"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E18:H18"/>
     <mergeCell ref="E21:H21"/>
@@ -2126,9 +2128,9 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="E23:H23"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A13:L13"/>
     <mergeCell ref="E20:H20"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="E19:H19"/>
@@ -2137,9 +2139,9 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E27:H27"/>
   </mergeCells>
